--- a/output/pdf_financials_xlsx/ASG.xlsx
+++ b/output/pdf_financials_xlsx/ASG.xlsx
@@ -1845,22 +1845,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.262896</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.579631</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.192842</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.012665</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.856504</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.444741</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>1.710146</v>
@@ -1943,22 +1943,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.262896</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.579631</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.192842</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.012665</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.856504</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.444741</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>1.710146</v>
@@ -2531,22 +2531,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.475641</v>
+        <v>0.212745</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.7849739999999999</v>
+        <v>0.205343</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.511228</v>
+        <v>0.318386</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.484524</v>
+        <v>0.471859</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.075805</v>
+        <v>0.219301</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>3.150054</v>
+        <v>2.705313</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>1.88938</v>
@@ -8406,7 +8406,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E31" s="5" t="n">

--- a/output/pdf_financials_xlsx/ASG.xlsx
+++ b/output/pdf_financials_xlsx/ASG.xlsx
@@ -5082,25 +5082,25 @@
         <v>0.780562</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0.274276</v>
+        <v>0.112374</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0.477168</v>
+        <v>0.112374</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0.496042</v>
+        <v>0.152645</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0.602225</v>
+        <v>0.266365</v>
       </c>
       <c r="K100" s="3" t="n">
         <v>0.73239</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0.658097</v>
+        <v>0.349329</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0.7034629999999999</v>
+        <v>0.367284</v>
       </c>
     </row>
     <row r="101">
@@ -5592,13 +5592,13 @@
         <v>0</v>
       </c>
       <c r="E112" s="3" t="n">
-        <v>0</v>
+        <v>0.173155</v>
       </c>
       <c r="F112" s="3" t="n">
-        <v>0</v>
+        <v>0.013774</v>
       </c>
       <c r="G112" s="3" t="n">
-        <v>0</v>
+        <v>0.002845</v>
       </c>
       <c r="H112" s="3" t="n">
         <v>0</v>
@@ -10656,7 +10656,11 @@
           <t>Depreciation of right of use asset 11</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -14690,7 +14694,11 @@
           <t>Depreciation of right of use asset 8</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr"/>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E110" t="inlineStr">
         <is>
           <t>-</t>
@@ -16864,7 +16872,11 @@
           <t>Depreciation of right of use asset 8</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>-</t>
@@ -17318,7 +17330,11 @@
           <t>Proceeds from sale of property and equipment</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -18588,7 +18604,11 @@
           <t>Additions to intangible assets 8</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>PurchaseOfIntangibles</t>
+        </is>
+      </c>
       <c r="E163" t="inlineStr">
         <is>
           <t>-</t>
